--- a/data/performance/daily/signal_list_2026-07-31.xlsx
+++ b/data/performance/daily/signal_list_2026-07-31.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-07-31.xlsx
+++ b/data/performance/daily/signal_list_2026-07-31.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>6875</v>
       </c>
       <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
         <v>6875</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>6975</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>1.45</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>121</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>118</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>123</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1.65</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-2.48</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>1455</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>1465</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>1475</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>1.37</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>2760</v>
       </c>
       <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
         <v>2750</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>2800</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>1.45</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.36</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>230</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>244</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>264</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>14.78</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>6.09</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>920</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>915</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>930</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-0.54</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>4200</v>
       </c>
       <c r="D11" t="n">
-        <v>4400</v>
+        <v/>
       </c>
       <c r="E11" t="n">
         <v>4400</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>4.76</v>
+      <c r="F11" t="n">
+        <v>4400</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>4.76</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H11" s="4" t="n">
+        <v>4.76</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>520</v>
       </c>
       <c r="D12" t="n">
-        <v>520</v>
+        <v/>
       </c>
       <c r="E12" t="n">
         <v>520</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
+      <c r="F12" t="n">
+        <v>520</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>454</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>454</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>478</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>5.29</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>340</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>344</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>346</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>1.76</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>1360</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>1335</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>1370</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-1.84</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,33 +1109,36 @@
         <v>410</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>420</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>430</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>4.88</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>2.44</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,33 +1159,36 @@
         <v>173</v>
       </c>
       <c r="D17" t="n">
+        <v/>
+      </c>
+      <c r="E17" t="n">
         <v>175</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>188</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>8.67</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>1.16</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1164,33 +1209,36 @@
         <v>171</v>
       </c>
       <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
         <v>157</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>220</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>28.65</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-8.19</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1211,33 +1259,36 @@
         <v>310</v>
       </c>
       <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
         <v>352</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>380</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>22.58</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>13.55</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1258,33 +1309,36 @@
         <v>97</v>
       </c>
       <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
         <v>97</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>103</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>6.19</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1305,33 +1359,36 @@
         <v>19075</v>
       </c>
       <c r="D21" t="n">
+        <v/>
+      </c>
+      <c r="E21" t="n">
         <v>19000</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>19175</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>0.52</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-0.39</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1352,33 +1409,36 @@
         <v>1225</v>
       </c>
       <c r="D22" t="n">
+        <v/>
+      </c>
+      <c r="E22" t="n">
         <v>1225</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>1245</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>1.63</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1399,33 +1459,36 @@
         <v>730</v>
       </c>
       <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
         <v>735</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>740</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>1.37</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1446,33 +1509,36 @@
         <v>24800</v>
       </c>
       <c r="D24" t="n">
+        <v/>
+      </c>
+      <c r="E24" t="n">
         <v>24575</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>24900</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-0.91</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1493,33 +1559,36 @@
         <v>1435</v>
       </c>
       <c r="D25" t="n">
+        <v/>
+      </c>
+      <c r="E25" t="n">
         <v>1430</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>1460</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>1.74</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>-0.35</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1540,33 +1609,36 @@
         <v>1560</v>
       </c>
       <c r="D26" t="n">
+        <v/>
+      </c>
+      <c r="E26" t="n">
         <v>1555</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>1565</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>0.32</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-0.32</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1587,33 +1659,36 @@
         <v>595</v>
       </c>
       <c r="D27" t="n">
-        <v>615</v>
+        <v/>
       </c>
       <c r="E27" t="n">
         <v>615</v>
       </c>
-      <c r="F27" s="4" t="n">
-        <v>3.36</v>
+      <c r="F27" t="n">
+        <v>615</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>3.36</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H27" s="4" t="n">
+        <v>3.36</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1634,33 +1709,36 @@
         <v>5700</v>
       </c>
       <c r="D28" t="n">
+        <v/>
+      </c>
+      <c r="E28" t="n">
         <v>5875</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>6000</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>5.26</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>3.07</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1681,33 +1759,36 @@
         <v>1780</v>
       </c>
       <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
         <v>1790</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>1805</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1728,33 +1809,36 @@
         <v>320</v>
       </c>
       <c r="D30" t="n">
+        <v/>
+      </c>
+      <c r="E30" t="n">
         <v>342</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>400</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>6.88</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1775,33 +1859,36 @@
         <v>1140</v>
       </c>
       <c r="D31" t="n">
+        <v/>
+      </c>
+      <c r="E31" t="n">
         <v>1140</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>1165</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>2.19</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1822,33 +1909,36 @@
         <v>1710</v>
       </c>
       <c r="D32" t="n">
+        <v/>
+      </c>
+      <c r="E32" t="n">
         <v>1705</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>1745</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>2.05</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>-0.29</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1869,33 +1959,36 @@
         <v>720</v>
       </c>
       <c r="D33" t="n">
+        <v/>
+      </c>
+      <c r="E33" t="n">
         <v>725</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>730</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1916,33 +2009,36 @@
         <v>1085</v>
       </c>
       <c r="D34" t="n">
+        <v/>
+      </c>
+      <c r="E34" t="n">
         <v>1070</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>1100</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>-1.38</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1963,33 +2059,36 @@
         <v>266</v>
       </c>
       <c r="D35" t="n">
+        <v/>
+      </c>
+      <c r="E35" t="n">
         <v>264</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>274</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>3.01</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>-0.75</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2010,33 +2109,36 @@
         <v>86</v>
       </c>
       <c r="D36" t="n">
+        <v/>
+      </c>
+      <c r="E36" t="n">
         <v>85</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>95</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>10.47</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>-1.16</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2057,33 +2159,36 @@
         <v>130</v>
       </c>
       <c r="D37" t="n">
+        <v/>
+      </c>
+      <c r="E37" t="n">
         <v>132</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>136</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>4.62</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2104,33 +2209,36 @@
         <v>151</v>
       </c>
       <c r="D38" t="n">
+        <v/>
+      </c>
+      <c r="E38" t="n">
         <v>147</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>154</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>1.99</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>-2.65</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2151,33 +2259,36 @@
         <v>1095</v>
       </c>
       <c r="D39" t="n">
+        <v/>
+      </c>
+      <c r="E39" t="n">
         <v>1095</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>1165</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>6.39</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2198,33 +2309,36 @@
         <v>230</v>
       </c>
       <c r="D40" t="n">
+        <v/>
+      </c>
+      <c r="E40" t="n">
         <v>254</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>268</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>16.52</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>10.43</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2245,33 +2359,36 @@
         <v>7475</v>
       </c>
       <c r="D41" t="n">
+        <v/>
+      </c>
+      <c r="E41" t="n">
         <v>7525</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>7850</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>5.02</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2292,33 +2409,36 @@
         <v>204</v>
       </c>
       <c r="D42" t="n">
+        <v/>
+      </c>
+      <c r="E42" t="n">
         <v>212</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>220</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>7.84</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>3.92</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2339,33 +2459,36 @@
         <v>8350</v>
       </c>
       <c r="D43" t="n">
-        <v>8350</v>
+        <v/>
       </c>
       <c r="E43" t="n">
         <v>8350</v>
       </c>
-      <c r="F43" s="4" t="n">
-        <v>0</v>
+      <c r="F43" t="n">
+        <v>8350</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2386,33 +2509,36 @@
         <v>820</v>
       </c>
       <c r="D44" t="n">
+        <v/>
+      </c>
+      <c r="E44" t="n">
         <v>800</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>825</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>0.61</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>-2.44</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2433,33 +2559,36 @@
         <v>156</v>
       </c>
       <c r="D45" t="n">
-        <v>169</v>
+        <v/>
       </c>
       <c r="E45" t="n">
         <v>169</v>
       </c>
-      <c r="F45" s="4" t="n">
-        <v>8.33</v>
+      <c r="F45" t="n">
+        <v>169</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>8.33</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H45" s="4" t="n">
+        <v>8.33</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2480,33 +2609,36 @@
         <v>63</v>
       </c>
       <c r="D46" t="n">
-        <v>64</v>
+        <v/>
       </c>
       <c r="E46" t="n">
         <v>64</v>
       </c>
-      <c r="F46" s="4" t="n">
-        <v>1.59</v>
+      <c r="F46" t="n">
+        <v>64</v>
       </c>
       <c r="G46" s="4" t="n">
         <v>1.59</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H46" s="4" t="n">
+        <v>1.59</v>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2527,33 +2659,36 @@
         <v>520</v>
       </c>
       <c r="D47" t="n">
+        <v/>
+      </c>
+      <c r="E47" t="n">
         <v>520</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>530</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>1.92</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2574,33 +2709,36 @@
         <v>580</v>
       </c>
       <c r="D48" t="n">
+        <v/>
+      </c>
+      <c r="E48" t="n">
         <v>530</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>575</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>-0.86</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>-8.619999999999999</v>
       </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2621,33 +2759,36 @@
         <v>855</v>
       </c>
       <c r="D49" t="n">
+        <v/>
+      </c>
+      <c r="E49" t="n">
         <v>790</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>870</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>1.75</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>-7.6</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2668,33 +2809,36 @@
         <v>141</v>
       </c>
       <c r="D50" t="n">
+        <v/>
+      </c>
+      <c r="E50" t="n">
         <v>144</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>163</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>15.6</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>2.13</v>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2715,33 +2859,36 @@
         <v>144</v>
       </c>
       <c r="D51" t="n">
+        <v/>
+      </c>
+      <c r="E51" t="n">
         <v>150</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>158</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>9.720000000000001</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>4.17</v>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2762,33 +2909,36 @@
         <v>160</v>
       </c>
       <c r="D52" t="n">
+        <v/>
+      </c>
+      <c r="E52" t="n">
         <v>163</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>191</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="G52" s="4" t="n">
         <v>19.38</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>1.88</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2809,33 +2959,36 @@
         <v>695</v>
       </c>
       <c r="D53" t="n">
+        <v/>
+      </c>
+      <c r="E53" t="n">
         <v>690</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>700</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="G53" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>-0.72</v>
       </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2856,33 +3009,36 @@
         <v>9275</v>
       </c>
       <c r="D54" t="n">
+        <v/>
+      </c>
+      <c r="E54" t="n">
         <v>9225</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>9375</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="G54" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="H54" s="4" t="n">
         <v>-0.54</v>
       </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2903,33 +3059,36 @@
         <v>8400</v>
       </c>
       <c r="D55" t="n">
+        <v/>
+      </c>
+      <c r="E55" t="n">
         <v>8675</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>8800</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>4.76</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>3.27</v>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2946,7 +3105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2954,12 +3113,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2989,45 +3149,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3048,33 +3213,36 @@
         <v>6875</v>
       </c>
       <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
         <v>6875</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>6975</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>1.45</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3095,33 +3263,36 @@
         <v>121</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>118</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>123</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1.65</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-2.48</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3142,33 +3313,36 @@
         <v>185</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>185</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>190</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>2.7</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3189,33 +3363,36 @@
         <v>2760</v>
       </c>
       <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
         <v>2750</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>2800</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>1.45</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.36</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3236,33 +3413,36 @@
         <v>230</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>244</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>264</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>14.78</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>6.09</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3283,33 +3463,36 @@
         <v>920</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>915</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>930</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>1.09</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-0.54</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3330,33 +3513,36 @@
         <v>163</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>160</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>168</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>3.07</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-1.84</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3377,33 +3563,36 @@
         <v>310</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>352</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>380</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>22.58</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>13.55</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3424,33 +3613,36 @@
         <v>97</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>97</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>103</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>6.19</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3471,33 +3663,36 @@
         <v>19075</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>19000</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>19175</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>0.52</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-0.39</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3518,33 +3713,36 @@
         <v>1225</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>1225</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>1245</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>1.63</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3565,33 +3763,36 @@
         <v>1330</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>1280</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>1330</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-3.76</v>
       </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3612,33 +3813,36 @@
         <v>181</v>
       </c>
       <c r="D17" t="n">
+        <v/>
+      </c>
+      <c r="E17" t="n">
         <v>177</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>190</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>4.97</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-2.21</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3659,33 +3863,36 @@
         <v>430</v>
       </c>
       <c r="D18" t="n">
-        <v>440</v>
+        <v/>
       </c>
       <c r="E18" t="n">
         <v>440</v>
       </c>
-      <c r="F18" s="4" t="n">
-        <v>2.33</v>
+      <c r="F18" t="n">
+        <v>440</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>2.33</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H18" s="4" t="n">
+        <v>2.33</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3706,33 +3913,36 @@
         <v>1600</v>
       </c>
       <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
         <v>1470</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>1600</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-8.119999999999999</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3753,33 +3963,36 @@
         <v>810</v>
       </c>
       <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
         <v>830</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>835</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>3.09</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>2.47</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3800,33 +4013,36 @@
         <v>1560</v>
       </c>
       <c r="D21" t="n">
+        <v/>
+      </c>
+      <c r="E21" t="n">
         <v>1555</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>1565</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>0.32</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-0.32</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3847,33 +4063,36 @@
         <v>175</v>
       </c>
       <c r="D22" t="n">
+        <v/>
+      </c>
+      <c r="E22" t="n">
         <v>191</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>193</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>10.29</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3894,33 +4113,36 @@
         <v>123</v>
       </c>
       <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
         <v>115</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>121</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>-1.63</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>-6.5</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3941,33 +4163,36 @@
         <v>197</v>
       </c>
       <c r="D24" t="n">
+        <v/>
+      </c>
+      <c r="E24" t="n">
         <v>204</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>208</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>5.58</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>3.55</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3988,33 +4213,36 @@
         <v>1780</v>
       </c>
       <c r="D25" t="n">
+        <v/>
+      </c>
+      <c r="E25" t="n">
         <v>1790</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>1805</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4035,33 +4263,36 @@
         <v>11600</v>
       </c>
       <c r="D26" t="n">
-        <v>12050</v>
+        <v/>
       </c>
       <c r="E26" t="n">
         <v>12050</v>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>3.88</v>
+      <c r="F26" t="n">
+        <v>12050</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>3.88</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H26" s="4" t="n">
+        <v>3.88</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4082,33 +4313,36 @@
         <v>1140</v>
       </c>
       <c r="D27" t="n">
+        <v/>
+      </c>
+      <c r="E27" t="n">
         <v>1140</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>1165</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>2.19</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4129,33 +4363,36 @@
         <v>1710</v>
       </c>
       <c r="D28" t="n">
+        <v/>
+      </c>
+      <c r="E28" t="n">
         <v>1705</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>1745</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>2.05</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>-0.29</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4176,33 +4413,36 @@
         <v>1935</v>
       </c>
       <c r="D29" t="n">
-        <v>2040</v>
+        <v/>
       </c>
       <c r="E29" t="n">
         <v>2040</v>
       </c>
-      <c r="F29" s="4" t="n">
-        <v>5.43</v>
+      <c r="F29" t="n">
+        <v>2040</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>5.43</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H29" s="4" t="n">
+        <v>5.43</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4223,33 +4463,36 @@
         <v>1085</v>
       </c>
       <c r="D30" t="n">
+        <v/>
+      </c>
+      <c r="E30" t="n">
         <v>1070</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>1100</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>-1.38</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4270,33 +4513,36 @@
         <v>260</v>
       </c>
       <c r="D31" t="n">
+        <v/>
+      </c>
+      <c r="E31" t="n">
         <v>264</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>304</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>16.92</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4317,33 +4563,36 @@
         <v>380</v>
       </c>
       <c r="D32" t="n">
+        <v/>
+      </c>
+      <c r="E32" t="n">
         <v>370</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>398</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>4.74</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>-2.63</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4364,33 +4613,36 @@
         <v>1235</v>
       </c>
       <c r="D33" t="n">
+        <v/>
+      </c>
+      <c r="E33" t="n">
         <v>1220</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>1240</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>-1.21</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4411,33 +4663,36 @@
         <v>164</v>
       </c>
       <c r="D34" t="n">
+        <v/>
+      </c>
+      <c r="E34" t="n">
         <v>167</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>182</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>10.98</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>1.83</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4458,33 +4713,36 @@
         <v>86</v>
       </c>
       <c r="D35" t="n">
+        <v/>
+      </c>
+      <c r="E35" t="n">
         <v>85</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>95</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>10.47</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>-1.16</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4505,33 +4763,36 @@
         <v>130</v>
       </c>
       <c r="D36" t="n">
+        <v/>
+      </c>
+      <c r="E36" t="n">
         <v>132</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>136</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>4.62</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>1.54</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4552,33 +4813,36 @@
         <v>154</v>
       </c>
       <c r="D37" t="n">
+        <v/>
+      </c>
+      <c r="E37" t="n">
         <v>148</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>155</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>-3.9</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4599,33 +4863,36 @@
         <v>151</v>
       </c>
       <c r="D38" t="n">
+        <v/>
+      </c>
+      <c r="E38" t="n">
         <v>147</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>154</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>1.99</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>-2.65</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4646,33 +4913,36 @@
         <v>230</v>
       </c>
       <c r="D39" t="n">
+        <v/>
+      </c>
+      <c r="E39" t="n">
         <v>254</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>268</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>16.52</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>10.43</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4693,33 +4963,36 @@
         <v>61</v>
       </c>
       <c r="D40" t="n">
+        <v/>
+      </c>
+      <c r="E40" t="n">
         <v>60</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>62</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>1.64</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>-1.64</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4740,33 +5013,36 @@
         <v>204</v>
       </c>
       <c r="D41" t="n">
+        <v/>
+      </c>
+      <c r="E41" t="n">
         <v>212</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>220</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>7.84</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>3.92</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4787,33 +5063,36 @@
         <v>75</v>
       </c>
       <c r="D42" t="n">
+        <v/>
+      </c>
+      <c r="E42" t="n">
         <v>73</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>76</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>-2.67</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4834,33 +5113,36 @@
         <v>156</v>
       </c>
       <c r="D43" t="n">
-        <v>169</v>
+        <v/>
       </c>
       <c r="E43" t="n">
         <v>169</v>
       </c>
-      <c r="F43" s="4" t="n">
-        <v>8.33</v>
+      <c r="F43" t="n">
+        <v>169</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>8.33</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H43" s="4" t="n">
+        <v>8.33</v>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4881,33 +5163,36 @@
         <v>580</v>
       </c>
       <c r="D44" t="n">
+        <v/>
+      </c>
+      <c r="E44" t="n">
         <v>530</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>575</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>-0.86</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>-8.619999999999999</v>
       </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4928,33 +5213,36 @@
         <v>855</v>
       </c>
       <c r="D45" t="n">
+        <v/>
+      </c>
+      <c r="E45" t="n">
         <v>790</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>870</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>1.75</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>-7.6</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4975,33 +5263,36 @@
         <v>290</v>
       </c>
       <c r="D46" t="n">
+        <v/>
+      </c>
+      <c r="E46" t="n">
         <v>308</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>316</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>6.21</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5022,33 +5313,36 @@
         <v>730</v>
       </c>
       <c r="D47" t="n">
+        <v/>
+      </c>
+      <c r="E47" t="n">
         <v>735</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>740</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>1.37</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5069,33 +5363,36 @@
         <v>141</v>
       </c>
       <c r="D48" t="n">
+        <v/>
+      </c>
+      <c r="E48" t="n">
         <v>144</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>163</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>15.6</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>2.13</v>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5116,33 +5413,36 @@
         <v>1085</v>
       </c>
       <c r="D49" t="n">
+        <v/>
+      </c>
+      <c r="E49" t="n">
         <v>1105</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>1190</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>9.68</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>1.84</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5163,33 +5463,36 @@
         <v>103</v>
       </c>
       <c r="D50" t="n">
+        <v/>
+      </c>
+      <c r="E50" t="n">
         <v>96</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>103</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>-6.8</v>
       </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5210,33 +5513,36 @@
         <v>310</v>
       </c>
       <c r="D51" t="n">
+        <v/>
+      </c>
+      <c r="E51" t="n">
         <v>322</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>328</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>5.81</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>3.87</v>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5257,33 +5563,36 @@
         <v>160</v>
       </c>
       <c r="D52" t="n">
+        <v/>
+      </c>
+      <c r="E52" t="n">
         <v>163</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>191</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="G52" s="4" t="n">
         <v>19.38</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>1.88</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5304,33 +5613,36 @@
         <v>695</v>
       </c>
       <c r="D53" t="n">
+        <v/>
+      </c>
+      <c r="E53" t="n">
         <v>690</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>700</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="G53" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>-0.72</v>
       </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5351,33 +5663,36 @@
         <v>144</v>
       </c>
       <c r="D54" t="n">
+        <v/>
+      </c>
+      <c r="E54" t="n">
         <v>138</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>148</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="G54" s="4" t="n">
         <v>2.78</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="H54" s="4" t="n">
         <v>-4.17</v>
       </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5398,33 +5713,36 @@
         <v>9275</v>
       </c>
       <c r="D55" t="n">
+        <v/>
+      </c>
+      <c r="E55" t="n">
         <v>9225</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>9375</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>-0.54</v>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5445,33 +5763,36 @@
         <v>3710</v>
       </c>
       <c r="D56" t="n">
+        <v/>
+      </c>
+      <c r="E56" t="n">
         <v>3790</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>3890</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="G56" s="4" t="n">
         <v>4.85</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="H56" s="4" t="n">
         <v>2.16</v>
       </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-07-31.xlsx
+++ b/data/performance/daily/signal_list_2026-07-31.xlsx
@@ -559,7 +559,7 @@
         <v>6875</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>6875</v>
       </c>
       <c r="E5" t="n">
         <v>6875</v>
@@ -609,7 +609,7 @@
         <v>121</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>122</v>
       </c>
       <c r="E6" t="n">
         <v>118</v>
@@ -659,7 +659,7 @@
         <v>1455</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>1405.34</v>
       </c>
       <c r="E7" t="n">
         <v>1465</v>
@@ -709,7 +709,7 @@
         <v>2760</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>2780</v>
       </c>
       <c r="E8" t="n">
         <v>2750</v>
@@ -759,7 +759,7 @@
         <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>232</v>
       </c>
       <c r="E9" t="n">
         <v>244</v>
@@ -809,7 +809,7 @@
         <v>920</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>930</v>
       </c>
       <c r="E10" t="n">
         <v>915</v>
@@ -859,7 +859,7 @@
         <v>4200</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>4200</v>
       </c>
       <c r="E11" t="n">
         <v>4400</v>
@@ -909,7 +909,7 @@
         <v>520</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>520</v>
       </c>
       <c r="E12" t="n">
         <v>520</v>
@@ -959,7 +959,7 @@
         <v>454</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>460</v>
       </c>
       <c r="E13" t="n">
         <v>454</v>
@@ -1009,7 +1009,7 @@
         <v>340</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>342</v>
       </c>
       <c r="E14" t="n">
         <v>344</v>
@@ -1059,7 +1059,7 @@
         <v>1360</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>1360</v>
       </c>
       <c r="E15" t="n">
         <v>1335</v>
@@ -1109,7 +1109,7 @@
         <v>410</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>422</v>
       </c>
       <c r="E16" t="n">
         <v>420</v>
@@ -1159,7 +1159,7 @@
         <v>173</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>173</v>
       </c>
       <c r="E17" t="n">
         <v>175</v>
@@ -1209,7 +1209,7 @@
         <v>171</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>189</v>
       </c>
       <c r="E18" t="n">
         <v>157</v>
@@ -1259,7 +1259,7 @@
         <v>310</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>320</v>
       </c>
       <c r="E19" t="n">
         <v>352</v>
@@ -1309,7 +1309,7 @@
         <v>97</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>99</v>
       </c>
       <c r="E20" t="n">
         <v>97</v>
@@ -1359,7 +1359,7 @@
         <v>19075</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>19125</v>
       </c>
       <c r="E21" t="n">
         <v>19000</v>
@@ -1409,7 +1409,7 @@
         <v>1225</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>1230</v>
       </c>
       <c r="E22" t="n">
         <v>1225</v>
@@ -1459,7 +1459,7 @@
         <v>730</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>735</v>
       </c>
       <c r="E23" t="n">
         <v>735</v>
@@ -1509,7 +1509,7 @@
         <v>24800</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>24875</v>
       </c>
       <c r="E24" t="n">
         <v>24575</v>
@@ -1559,7 +1559,7 @@
         <v>1435</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>1450</v>
       </c>
       <c r="E25" t="n">
         <v>1430</v>
@@ -1609,7 +1609,7 @@
         <v>1560</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>1560</v>
       </c>
       <c r="E26" t="n">
         <v>1555</v>
@@ -1659,7 +1659,7 @@
         <v>595</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>600</v>
       </c>
       <c r="E27" t="n">
         <v>615</v>
@@ -1709,7 +1709,7 @@
         <v>5700</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>5900</v>
       </c>
       <c r="E28" t="n">
         <v>5875</v>
@@ -1759,7 +1759,7 @@
         <v>1780</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>1740</v>
       </c>
       <c r="E29" t="n">
         <v>1790</v>
@@ -1809,7 +1809,7 @@
         <v>320</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>400</v>
       </c>
       <c r="E30" t="n">
         <v>342</v>
@@ -1859,7 +1859,7 @@
         <v>1140</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>1145</v>
       </c>
       <c r="E31" t="n">
         <v>1140</v>
@@ -1909,7 +1909,7 @@
         <v>1710</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>1710</v>
       </c>
       <c r="E32" t="n">
         <v>1705</v>
@@ -1959,7 +1959,7 @@
         <v>720</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>725</v>
       </c>
       <c r="E33" t="n">
         <v>725</v>
@@ -2009,7 +2009,7 @@
         <v>1085</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>1080.18</v>
       </c>
       <c r="E34" t="n">
         <v>1070</v>
@@ -2059,7 +2059,7 @@
         <v>266</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>268</v>
       </c>
       <c r="E35" t="n">
         <v>264</v>
@@ -2109,7 +2109,7 @@
         <v>86</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>88</v>
       </c>
       <c r="E36" t="n">
         <v>85</v>
@@ -2159,7 +2159,7 @@
         <v>130</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>131</v>
       </c>
       <c r="E37" t="n">
         <v>132</v>
@@ -2209,7 +2209,7 @@
         <v>151</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>145</v>
       </c>
       <c r="E38" t="n">
         <v>147</v>
@@ -2259,7 +2259,7 @@
         <v>1095</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>1130</v>
       </c>
       <c r="E39" t="n">
         <v>1095</v>
@@ -2309,7 +2309,7 @@
         <v>230</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>230</v>
       </c>
       <c r="E40" t="n">
         <v>254</v>
@@ -2359,7 +2359,7 @@
         <v>7475</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>7850</v>
       </c>
       <c r="E41" t="n">
         <v>7525</v>
@@ -2409,7 +2409,7 @@
         <v>204</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>206</v>
       </c>
       <c r="E42" t="n">
         <v>212</v>
@@ -2459,7 +2459,7 @@
         <v>8350</v>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>8275</v>
       </c>
       <c r="E43" t="n">
         <v>8350</v>
@@ -2509,7 +2509,7 @@
         <v>820</v>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>825</v>
       </c>
       <c r="E44" t="n">
         <v>800</v>
@@ -2559,7 +2559,7 @@
         <v>156</v>
       </c>
       <c r="D45" t="n">
-        <v/>
+        <v>150</v>
       </c>
       <c r="E45" t="n">
         <v>169</v>
@@ -2609,7 +2609,7 @@
         <v>63</v>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>64</v>
       </c>
       <c r="E46" t="n">
         <v>64</v>
@@ -2659,7 +2659,7 @@
         <v>520</v>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>525</v>
       </c>
       <c r="E47" t="n">
         <v>520</v>
@@ -2709,7 +2709,7 @@
         <v>580</v>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>560</v>
       </c>
       <c r="E48" t="n">
         <v>530</v>
@@ -2759,7 +2759,7 @@
         <v>855</v>
       </c>
       <c r="D49" t="n">
-        <v/>
+        <v>870</v>
       </c>
       <c r="E49" t="n">
         <v>790</v>
@@ -2809,7 +2809,7 @@
         <v>141</v>
       </c>
       <c r="D50" t="n">
-        <v/>
+        <v>146</v>
       </c>
       <c r="E50" t="n">
         <v>144</v>
@@ -2859,7 +2859,7 @@
         <v>144</v>
       </c>
       <c r="D51" t="n">
-        <v/>
+        <v>147</v>
       </c>
       <c r="E51" t="n">
         <v>150</v>
@@ -2909,7 +2909,7 @@
         <v>160</v>
       </c>
       <c r="D52" t="n">
-        <v/>
+        <v>169</v>
       </c>
       <c r="E52" t="n">
         <v>163</v>
@@ -2959,7 +2959,7 @@
         <v>695</v>
       </c>
       <c r="D53" t="n">
-        <v/>
+        <v>700</v>
       </c>
       <c r="E53" t="n">
         <v>690</v>
@@ -3009,7 +3009,7 @@
         <v>9275</v>
       </c>
       <c r="D54" t="n">
-        <v/>
+        <v>9300</v>
       </c>
       <c r="E54" t="n">
         <v>9225</v>
@@ -3059,7 +3059,7 @@
         <v>8400</v>
       </c>
       <c r="D55" t="n">
-        <v/>
+        <v>8625</v>
       </c>
       <c r="E55" t="n">
         <v>8675</v>
@@ -3213,7 +3213,7 @@
         <v>6875</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>6875</v>
       </c>
       <c r="E5" t="n">
         <v>6875</v>
@@ -3263,7 +3263,7 @@
         <v>121</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>122</v>
       </c>
       <c r="E6" t="n">
         <v>118</v>
@@ -3313,7 +3313,7 @@
         <v>185</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>185</v>
       </c>
       <c r="E7" t="n">
         <v>185</v>
@@ -3363,7 +3363,7 @@
         <v>2760</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>2780</v>
       </c>
       <c r="E8" t="n">
         <v>2750</v>
@@ -3413,7 +3413,7 @@
         <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>232</v>
       </c>
       <c r="E9" t="n">
         <v>244</v>
@@ -3463,7 +3463,7 @@
         <v>920</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>930</v>
       </c>
       <c r="E10" t="n">
         <v>915</v>
@@ -3513,7 +3513,7 @@
         <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>165</v>
       </c>
       <c r="E11" t="n">
         <v>160</v>
@@ -3563,7 +3563,7 @@
         <v>310</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>320</v>
       </c>
       <c r="E12" t="n">
         <v>352</v>
@@ -3613,7 +3613,7 @@
         <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>99</v>
       </c>
       <c r="E13" t="n">
         <v>97</v>
@@ -3663,7 +3663,7 @@
         <v>19075</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>19125</v>
       </c>
       <c r="E14" t="n">
         <v>19000</v>
@@ -3713,7 +3713,7 @@
         <v>1225</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>1230</v>
       </c>
       <c r="E15" t="n">
         <v>1225</v>
@@ -3763,7 +3763,7 @@
         <v>1330</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>1330</v>
       </c>
       <c r="E16" t="n">
         <v>1280</v>
@@ -3813,7 +3813,7 @@
         <v>181</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>182</v>
       </c>
       <c r="E17" t="n">
         <v>177</v>
@@ -3863,7 +3863,7 @@
         <v>430</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>430</v>
       </c>
       <c r="E18" t="n">
         <v>440</v>
@@ -3913,7 +3913,7 @@
         <v>1600</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>1595</v>
       </c>
       <c r="E19" t="n">
         <v>1470</v>
@@ -3963,7 +3963,7 @@
         <v>810</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>810</v>
       </c>
       <c r="E20" t="n">
         <v>830</v>
@@ -4013,7 +4013,7 @@
         <v>1560</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>1560</v>
       </c>
       <c r="E21" t="n">
         <v>1555</v>
@@ -4063,7 +4063,7 @@
         <v>175</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>168</v>
       </c>
       <c r="E22" t="n">
         <v>191</v>
@@ -4113,7 +4113,7 @@
         <v>123</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>121</v>
       </c>
       <c r="E23" t="n">
         <v>115</v>
@@ -4163,7 +4163,7 @@
         <v>197</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>197</v>
       </c>
       <c r="E24" t="n">
         <v>204</v>
@@ -4213,7 +4213,7 @@
         <v>1780</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>1740</v>
       </c>
       <c r="E25" t="n">
         <v>1790</v>
@@ -4263,7 +4263,7 @@
         <v>11600</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>11600</v>
       </c>
       <c r="E26" t="n">
         <v>12050</v>
@@ -4313,7 +4313,7 @@
         <v>1140</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>1145</v>
       </c>
       <c r="E27" t="n">
         <v>1140</v>
@@ -4363,7 +4363,7 @@
         <v>1710</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>1710</v>
       </c>
       <c r="E28" t="n">
         <v>1705</v>
@@ -4413,7 +4413,7 @@
         <v>1935</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>1870</v>
       </c>
       <c r="E29" t="n">
         <v>2040</v>
@@ -4463,7 +4463,7 @@
         <v>1085</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>1080.18</v>
       </c>
       <c r="E30" t="n">
         <v>1070</v>
@@ -4513,7 +4513,7 @@
         <v>260</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>264</v>
       </c>
       <c r="E31" t="n">
         <v>264</v>
@@ -4563,7 +4563,7 @@
         <v>380</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>388</v>
       </c>
       <c r="E32" t="n">
         <v>370</v>
@@ -4613,7 +4613,7 @@
         <v>1235</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>1240</v>
       </c>
       <c r="E33" t="n">
         <v>1220</v>
@@ -4663,7 +4663,7 @@
         <v>164</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>164</v>
       </c>
       <c r="E34" t="n">
         <v>167</v>
@@ -4713,7 +4713,7 @@
         <v>86</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>88</v>
       </c>
       <c r="E35" t="n">
         <v>85</v>
@@ -4763,7 +4763,7 @@
         <v>130</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>131</v>
       </c>
       <c r="E36" t="n">
         <v>132</v>
@@ -4813,7 +4813,7 @@
         <v>154</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>154</v>
       </c>
       <c r="E37" t="n">
         <v>148</v>
@@ -4863,7 +4863,7 @@
         <v>151</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>145</v>
       </c>
       <c r="E38" t="n">
         <v>147</v>
@@ -4913,7 +4913,7 @@
         <v>230</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>230</v>
       </c>
       <c r="E39" t="n">
         <v>254</v>
@@ -4963,7 +4963,7 @@
         <v>61</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>60.68</v>
       </c>
       <c r="E40" t="n">
         <v>60</v>
@@ -5013,7 +5013,7 @@
         <v>204</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>206</v>
       </c>
       <c r="E41" t="n">
         <v>212</v>
@@ -5063,7 +5063,7 @@
         <v>75</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>75</v>
       </c>
       <c r="E42" t="n">
         <v>73</v>
@@ -5113,7 +5113,7 @@
         <v>156</v>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>150</v>
       </c>
       <c r="E43" t="n">
         <v>169</v>
@@ -5163,7 +5163,7 @@
         <v>580</v>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>560</v>
       </c>
       <c r="E44" t="n">
         <v>530</v>
@@ -5213,7 +5213,7 @@
         <v>855</v>
       </c>
       <c r="D45" t="n">
-        <v/>
+        <v>870</v>
       </c>
       <c r="E45" t="n">
         <v>790</v>
@@ -5263,7 +5263,7 @@
         <v>290</v>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>288</v>
       </c>
       <c r="E46" t="n">
         <v>308</v>
@@ -5313,7 +5313,7 @@
         <v>730</v>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>735</v>
       </c>
       <c r="E47" t="n">
         <v>735</v>
@@ -5363,7 +5363,7 @@
         <v>141</v>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>146</v>
       </c>
       <c r="E48" t="n">
         <v>144</v>
@@ -5413,7 +5413,7 @@
         <v>1085</v>
       </c>
       <c r="D49" t="n">
-        <v/>
+        <v>1095</v>
       </c>
       <c r="E49" t="n">
         <v>1105</v>
@@ -5463,7 +5463,7 @@
         <v>103</v>
       </c>
       <c r="D50" t="n">
-        <v/>
+        <v>102</v>
       </c>
       <c r="E50" t="n">
         <v>96</v>
@@ -5513,7 +5513,7 @@
         <v>310</v>
       </c>
       <c r="D51" t="n">
-        <v/>
+        <v>314</v>
       </c>
       <c r="E51" t="n">
         <v>322</v>
@@ -5563,7 +5563,7 @@
         <v>160</v>
       </c>
       <c r="D52" t="n">
-        <v/>
+        <v>169</v>
       </c>
       <c r="E52" t="n">
         <v>163</v>
@@ -5613,7 +5613,7 @@
         <v>695</v>
       </c>
       <c r="D53" t="n">
-        <v/>
+        <v>700</v>
       </c>
       <c r="E53" t="n">
         <v>690</v>
@@ -5663,7 +5663,7 @@
         <v>144</v>
       </c>
       <c r="D54" t="n">
-        <v/>
+        <v>148</v>
       </c>
       <c r="E54" t="n">
         <v>138</v>
@@ -5713,7 +5713,7 @@
         <v>9275</v>
       </c>
       <c r="D55" t="n">
-        <v/>
+        <v>9300</v>
       </c>
       <c r="E55" t="n">
         <v>9225</v>
@@ -5763,7 +5763,7 @@
         <v>3710</v>
       </c>
       <c r="D56" t="n">
-        <v/>
+        <v>3730</v>
       </c>
       <c r="E56" t="n">
         <v>3790</v>
